--- a/assets/libreoffice_calc_njc/f7c9725b-9f02-4131-a007-68de65161a3c/Region_SalesVsTarget_Chart.xlsx
+++ b/assets/libreoffice_calc_njc/f7c9725b-9f02-4131-a007-68de65161a3c/Region_SalesVsTarget_Chart.xlsx
@@ -446,11 +446,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="36127490"/>
-        <c:axId val="71059923"/>
+        <c:axId val="86321725"/>
+        <c:axId val="72705620"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="36127490"/>
+        <c:axId val="86321725"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -478,7 +478,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71059923"/>
+        <c:crossAx val="72705620"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -486,7 +486,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71059923"/>
+        <c:axId val="72705620"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -523,367 +523,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36127490"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="b3b3b3"/>
-          </a:solidFill>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="ffffff"/>
-    </a:solidFill>
-    <a:ln w="0">
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:rPr>
-              <a:t>Sales vs Target</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Sales ($)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="004586"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>West</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Central</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>85000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>72000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>91000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>68000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>78000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Target ($)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="ff420e"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>West</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Central</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$C$2:$C$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>90000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>75000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>85000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>70000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>80000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:gapWidth val="100"/>
-        <c:overlap val="0"/>
-        <c:axId val="84359434"/>
-        <c:axId val="40817721"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="84359434"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
-            </a:solidFill>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="40817721"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="40817721"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
-            </a:solidFill>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="84359434"/>
+        <c:crossAx val="86321725"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -942,9 +582,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>69840</xdr:colOff>
+      <xdr:colOff>69480</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>150480</xdr:rowOff>
+      <xdr:rowOff>150120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -953,42 +593,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="360" y="360"/>
-        <a:ext cx="5767920" cy="3238920"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>36360</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>36000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>479520</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>36720</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name=""/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="2314800" y="36000"/>
-        <a:ext cx="5759280" cy="3239280"/>
+        <a:ext cx="5771880" cy="3238560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1007,7 +612,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -1102,6 +707,5 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/assets/libreoffice_calc_njc/f7c9725b-9f02-4131-a007-68de65161a3c/Region_SalesVsTarget_Chart.xlsx
+++ b/assets/libreoffice_calc_njc/f7c9725b-9f02-4131-a007-68de65161a3c/Region_SalesVsTarget_Chart.xlsx
@@ -446,11 +446,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="86321725"/>
-        <c:axId val="72705620"/>
+        <c:axId val="60360786"/>
+        <c:axId val="29982695"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="86321725"/>
+        <c:axId val="60360786"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -478,7 +478,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72705620"/>
+        <c:crossAx val="29982695"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -486,7 +486,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72705620"/>
+        <c:axId val="29982695"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -523,7 +523,270 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86321725"/>
+        <c:crossAx val="60360786"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Sales vs Target</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales ($)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Central</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>85000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>72000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>78000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="100"/>
+        <c:overlap val="0"/>
+        <c:axId val="45450737"/>
+        <c:axId val="28401585"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="45450737"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="28401585"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="28401585"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="45450737"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -582,9 +845,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>69480</xdr:colOff>
+      <xdr:colOff>68040</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>150120</xdr:rowOff>
+      <xdr:rowOff>148680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -593,7 +856,42 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="360" y="360"/>
-        <a:ext cx="5771880" cy="3238560"/>
+        <a:ext cx="5775120" cy="3237120"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>36360</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>36000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>479160</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>36360</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="2314800" y="36000"/>
+        <a:ext cx="5758920" cy="3238920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -612,7 +910,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -707,5 +1005,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/assets/libreoffice_calc_njc/f7c9725b-9f02-4131-a007-68de65161a3c/Region_SalesVsTarget_Chart.xlsx
+++ b/assets/libreoffice_calc_njc/f7c9725b-9f02-4131-a007-68de65161a3c/Region_SalesVsTarget_Chart.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Sales vs Target" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -54,7 +55,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -79,6 +80,11 @@
     </font>
     <font>
       <sz val="13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -250,221 +256,21 @@
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Sales ($)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="004586"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>West</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Central</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$B$2:$B$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>85000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>72000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>91000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>68000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>78000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Target ($)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="ff420e"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$A$2:$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>West</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Central</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$C$2:$C$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>90000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>75000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>85000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>70000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>80000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:gapWidth val="100"/>
-        <c:overlap val="0"/>
-        <c:axId val="60360786"/>
-        <c:axId val="29982695"/>
+        <c:axId val="62017762"/>
+        <c:axId val="54247891"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="60360786"/>
+        <c:axId val="62017762"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="none"/>
         <c:spPr>
           <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
-            </a:solidFill>
+            <a:noFill/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -472,44 +278,28 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
+              <a:defRPr b="0" sz="1800" spc="-1"/>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29982695"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="54247891"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29982695"/>
+        <c:axId val="54247891"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="none"/>
         <c:spPr>
           <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
-            </a:solidFill>
+            <a:noFill/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -517,15 +307,12 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
+              <a:defRPr b="0" sz="1800" spc="-1"/>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60360786"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossAx val="62017762"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -583,6 +370,288 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
+              <a:defRPr b="0" sz="1100" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1100" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Sales vs Target</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:axId val="4132484"/>
+        <c:axId val="61206923"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="4132484"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1800" spc="-1"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="61206923"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="61206923"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1800" spc="-1"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="4132484"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Sales vs Target</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:axId val="23615924"/>
+        <c:axId val="35997828"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="23615924"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1800" spc="-1"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="35997828"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="35997828"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1800" spc="-1"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="23615924"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
               <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
                 <a:latin typeface="Arial"/>
               </a:defRPr>
@@ -615,7 +684,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
+              <c:f>Sheet1!$B$1:$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -707,13 +776,110 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1:$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Target ($)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Central</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>90000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>85000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="45450737"/>
-        <c:axId val="28401585"/>
+        <c:axId val="45421703"/>
+        <c:axId val="33956"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="45450737"/>
+        <c:axId val="45421703"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -741,7 +907,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28401585"/>
+        <c:crossAx val="33956"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -749,7 +915,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28401585"/>
+        <c:axId val="33956"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -786,7 +952,1228 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45450737"/>
+        <c:crossAx val="45421703"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Sales vs Target</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:axId val="44265327"/>
+        <c:axId val="57486330"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="44265327"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1800" spc="-1"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="57486330"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="57486330"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="none"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1800" spc="-1"/>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="44265327"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Sales vs Target</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales ($)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Central</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>85000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>72000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>78000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Target ($)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Central</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>90000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>85000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="100"/>
+        <c:overlap val="0"/>
+        <c:axId val="57695054"/>
+        <c:axId val="18184957"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="57695054"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="18184957"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="18184957"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="57695054"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Sales vs Target</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales ($)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Central</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>85000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>72000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>78000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Target ($)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Central</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>90000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>85000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="100"/>
+        <c:overlap val="0"/>
+        <c:axId val="95566421"/>
+        <c:axId val="89575487"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="95566421"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="89575487"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="89575487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="95566421"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:rPr>
+              <a:t>Sales vs Target</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sales ($)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Central</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>85000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>72000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>91000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>68000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>78000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Target ($)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>West</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Central</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>90000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>85000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="100"/>
+        <c:overlap val="0"/>
+        <c:axId val="76380269"/>
+        <c:axId val="1311182"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="76380269"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1311182"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1311182"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="76380269"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -838,16 +2225,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>360</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>36360</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>360</xdr:rowOff>
+      <xdr:rowOff>36000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>68040</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>148680</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>98280</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>20520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -855,12 +2242,72 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="360" y="360"/>
-        <a:ext cx="5775120" cy="3237120"/>
+        <a:off x="851760" y="36000"/>
+        <a:ext cx="5769360" cy="3235680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>36360</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>36000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>93960</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>20880</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="851760" y="36000"/>
+        <a:ext cx="5765040" cy="3236040"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>36360</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>36000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>89640</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>21240</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="851760" y="36000"/>
+        <a:ext cx="5760720" cy="3236400"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -873,6 +2320,71 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>39600</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>105840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>104040</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>88560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="855000" y="756000"/>
+        <a:ext cx="5771880" cy="3233880"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>301680</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>160200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>353520</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>148320</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4378320" y="648000"/>
+        <a:ext cx="5759280" cy="3239280"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>36360</xdr:colOff>
       <xdr:row>0</xdr:row>
@@ -880,22 +2392,82 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>479160</xdr:colOff>
+      <xdr:colOff>475560</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>36360</xdr:rowOff>
+      <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvPr id="5" name=""/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="2314800" y="36000"/>
-        <a:ext cx="5758920" cy="3238920"/>
+        <a:ext cx="5755320" cy="3235320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>36360</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>36000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>477360</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>34560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="2314800" y="36000"/>
+        <a:ext cx="5757120" cy="3237120"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>36360</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>36000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>478080</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>35280</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="2314800" y="36000"/>
+        <a:ext cx="5757840" cy="3237840"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -924,6 +2496,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
